--- a/tarefa_livia/dados/saude_mental_brasil_estudantes.csv.xlsx
+++ b/tarefa_livia/dados/saude_mental_brasil_estudantes.csv.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0890c980b84ff306/Documentos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0890c980b84ff306/Desktop/senac/Conectamente/tarefa_livia/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{006A8110-8798-4895-A0CD-367B173A676F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -516,7 +516,7 @@
     <col min="1" max="3" width="25.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -560,7 +560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="100.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -571,7 +571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
@@ -582,7 +582,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
@@ -593,7 +593,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -604,7 +604,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
@@ -615,7 +615,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
